--- a/backend/data/templates/pipeline.xlsx
+++ b/backend/data/templates/pipeline.xlsx
@@ -81,7 +81,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -100,6 +100,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -502,12 +505,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Probablity</t>
+          <t>Probability (%)</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Loan Type</t>
+          <t>Loan Type.</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -517,7 +520,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Login Amount</t>
+          <t>Login Loan Amount</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -542,7 +545,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>Service Region</t>
+          <t>Service Location</t>
         </is>
       </c>
     </row>
@@ -557,10 +560,8 @@
           <t>Login</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>for Login it should be 50%</t>
-        </is>
+      <c r="C3" s="7" t="n">
+        <v>50</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
